--- a/adp_data.xlsx
+++ b/adp_data.xlsx
@@ -466,266 +466,266 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09854681352667871</v>
+        <v>0.07573061107029044</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05457574538978438</v>
+        <v>0.02009588608502533</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07573061107029044</v>
+        <v>0.0718896380546008</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02009588608502533</v>
+        <v>-0.0172215843857626</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0718896380546008</v>
+        <v>0.09754843393172674</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0172215843857626</v>
+        <v>0.2267899178963084</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B5" t="n">
-        <v>0.09754843393172674</v>
+        <v>0.06874617552183881</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2267899178963084</v>
+        <v>0.1059777160369979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06874617552183881</v>
+        <v>0.06190454620946806</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1059777160369979</v>
+        <v>0.08869814020029398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B7" t="n">
-        <v>0.06190454620946806</v>
+        <v>0.08525470787059675</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08869814020029398</v>
+        <v>0.1029130099196696</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B8" t="n">
-        <v>0.08525470787059675</v>
+        <v>0.1236270984569243</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1029130099196696</v>
+        <v>0.1627780792186728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1236270984569243</v>
+        <v>0.1023934468193932</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1627780792186728</v>
+        <v>0.06842675486116168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1023934468193932</v>
+        <v>0.03158916040524318</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06842675486116168</v>
+        <v>0.03418998233517545</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03158916040524318</v>
+        <v>0.135339363453868</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03418998233517545</v>
+        <v>0.09399031614925057</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B12" t="n">
-        <v>0.135339363453868</v>
+        <v>0.1456686114177153</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09399031614925057</v>
+        <v>0.1223572261901396</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1456686114177153</v>
+        <v>0.1657007040405389</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1223572261901396</v>
+        <v>0.116523617347819</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1657007040405389</v>
+        <v>0.1527014686288242</v>
       </c>
       <c r="C14" t="n">
-        <v>0.116523617347819</v>
+        <v>0.133420387770733</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1527014686288242</v>
+        <v>0.1315415776020679</v>
       </c>
       <c r="C15" t="n">
-        <v>0.133420387770733</v>
+        <v>0.0935533253954679</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1315415776020679</v>
+        <v>0.1388329078776396</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0935533253954679</v>
+        <v>0.07930438723200428</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1388329078776396</v>
+        <v>0.06261180679785205</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07930438723200428</v>
+        <v>-0.01132022074430417</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06261180679785205</v>
+        <v>0.1095021006525476</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.01132022074430417</v>
+        <v>0.0849112677252295</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1095021006525476</v>
+        <v>0.04464584682009054</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0849112677252295</v>
+        <v>0.07069935804981942</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B20" t="n">
-        <v>0.04464584682009054</v>
+        <v>0.02156919621274511</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07069935804981942</v>
+        <v>-0.02260781099869824</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02156919621274511</v>
+        <v>-0.01710291493158822</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.02260781099869824</v>
+        <v>-0.08762507773192318</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.01710291493158822</v>
+        <v>0.07734814847870641</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.08762507773192318</v>
+        <v>0.06224007695136979</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B23" t="n">
-        <v>0.07734814847870641</v>
+        <v>-0.002229472135317767</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06224007695136979</v>
+        <v>-0.03958268540247278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.002229472135317767</v>
+        <v>-0.02155204447152892</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.03958268540247278</v>
+        <v>-0.05091217649554336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.02378156631340778</v>
+        <v>0.03122003434203879</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.05374063074530255</v>
+        <v>-0.04244842516342162</v>
       </c>
     </row>
   </sheetData>

--- a/adp_data.xlsx
+++ b/adp_data.xlsx
@@ -466,266 +466,266 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45231</v>
+        <v>45292</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07573061107029044</v>
+        <v>0.09754843393172674</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02009588608502533</v>
+        <v>0.2267899178963084</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45261</v>
+        <v>45323</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0718896380546008</v>
+        <v>0.06874617552183881</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0172215843857626</v>
+        <v>0.1059777160369979</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45292</v>
+        <v>45352</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09754843393172674</v>
+        <v>0.06190454620946806</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2267899178963084</v>
+        <v>0.08869814020029398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45323</v>
+        <v>45383</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06874617552183881</v>
+        <v>0.08525470787059675</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1059777160369979</v>
+        <v>0.1029130099196696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45352</v>
+        <v>45413</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06190454620946806</v>
+        <v>0.1236270984569243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08869814020029398</v>
+        <v>0.1627780792186728</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45383</v>
+        <v>45444</v>
       </c>
       <c r="B7" t="n">
-        <v>0.08525470787059675</v>
+        <v>0.1023934468193932</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1029130099196696</v>
+        <v>0.06842675486116168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45413</v>
+        <v>45474</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1236270984569243</v>
+        <v>0.03158916040524318</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1627780792186728</v>
+        <v>0.03418998233517545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45444</v>
+        <v>45505</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1023934468193932</v>
+        <v>0.135339363453868</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06842675486116168</v>
+        <v>0.09399031614925057</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45474</v>
+        <v>45536</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03158916040524318</v>
+        <v>0.1456686114177153</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03418998233517545</v>
+        <v>0.1223572261901396</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45505</v>
+        <v>45566</v>
       </c>
       <c r="B11" t="n">
-        <v>0.135339363453868</v>
+        <v>0.1657007040405389</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09399031614925057</v>
+        <v>0.116523617347819</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45536</v>
+        <v>45597</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1456686114177153</v>
+        <v>0.1527014686288242</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1223572261901396</v>
+        <v>0.133420387770733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45566</v>
+        <v>45627</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1657007040405389</v>
+        <v>0.1315415776020679</v>
       </c>
       <c r="C13" t="n">
-        <v>0.116523617347819</v>
+        <v>0.0935533253954679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45597</v>
+        <v>45658</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1527014686288242</v>
+        <v>0.1388329078776396</v>
       </c>
       <c r="C14" t="n">
-        <v>0.133420387770733</v>
+        <v>0.07930438723200428</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45627</v>
+        <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1315415776020679</v>
+        <v>0.06261180679785205</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0935533253954679</v>
+        <v>-0.01132022074430417</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45658</v>
+        <v>45717</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1388329078776396</v>
+        <v>0.1095021006525476</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07930438723200428</v>
+        <v>0.0849112677252295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45689</v>
+        <v>45748</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06261180679785205</v>
+        <v>0.04464584682009054</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.01132022074430417</v>
+        <v>0.07069935804981942</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45717</v>
+        <v>45778</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1095021006525476</v>
+        <v>0.02156919621274511</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0849112677252295</v>
+        <v>-0.02260781099869824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45748</v>
+        <v>45809</v>
       </c>
       <c r="B19" t="n">
-        <v>0.04464584682009054</v>
+        <v>-0.01710291493158822</v>
       </c>
       <c r="C19" t="n">
-        <v>0.07069935804981942</v>
+        <v>-0.08762507773192318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45778</v>
+        <v>45839</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02156919621274511</v>
+        <v>0.07734814847870641</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.02260781099869824</v>
+        <v>0.06224007695136979</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45809</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.01710291493158822</v>
+        <v>-0.002229472135317767</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.08762507773192318</v>
+        <v>-0.03958268540247278</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45839</v>
+        <v>45901</v>
       </c>
       <c r="B22" t="n">
-        <v>0.07734814847870641</v>
+        <v>-0.02155204447152892</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06224007695136979</v>
+        <v>-0.05091217649554336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45870</v>
+        <v>45931</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.002229472135317767</v>
+        <v>0.03493670509704394</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.03958268540247278</v>
+        <v>-0.06791748026148126</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45901</v>
+        <v>45962</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.02155204447152892</v>
+        <v>-0.02154916181191791</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.05091217649554336</v>
+        <v>-0.1246000056636332</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03122003434203879</v>
+        <v>0.03047262294959552</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.04244842516342162</v>
+        <v>0.01134140463296962</v>
       </c>
     </row>
   </sheetData>
